--- a/artfynd/A 51957-2025 artfynd.xlsx
+++ b/artfynd/A 51957-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>110049532</v>
+        <v>104157791</v>
       </c>
       <c r="B2" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,34 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Vitträskbäcken-Pålkem, Nb</t>
+          <t>Pålkem, Nb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>800059.4823708398</v>
+        <v>799676</v>
       </c>
       <c r="R2" t="n">
-        <v>7374459.608761461</v>
+        <v>7374614</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,22 +740,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2022-09-23</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-08-23</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2022-09-23</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-08-23</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Påträffad i samband med Sveaskogs naturvärdesbedömning</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,15 +765,500 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>110049223</v>
+      </c>
+      <c r="B3" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Vitträskbäcken-Pålkem, Nb</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>800743</v>
+      </c>
+      <c r="R3" t="n">
+        <v>7374103</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2022-09-27</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2022-09-27</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
           <t>Robert Sandberg</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AX3" t="inlineStr">
         <is>
           <t>per-erik mukka</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr"/>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>110049228</v>
+      </c>
+      <c r="B4" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Vitträskbäcken-Pålkem, Nb</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>800451</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7374151</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2022-09-27</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2022-09-27</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Robert Sandberg</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>per-erik mukka</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>110049292</v>
+      </c>
+      <c r="B5" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Vitträskbäcken-Pålkem, Nb</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>800203</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7374230</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2022-09-27</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2022-09-27</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Robert Sandberg</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>per-erik mukka</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>110049524</v>
+      </c>
+      <c r="B6" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Vitträskbäcken-Pålkem, Nb</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>799789</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7374642</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2022-09-23</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2022-09-23</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Robert Sandberg</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>per-erik mukka</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>110049532</v>
+      </c>
+      <c r="B7" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Vitträskbäcken-Pålkem, Nb</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>800059</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7374459</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2022-09-23</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2022-09-23</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Robert Sandberg</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>per-erik mukka</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 51957-2025 artfynd.xlsx
+++ b/artfynd/A 51957-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1165,10 +1165,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>110049223</v>
+        <v>135449034</v>
       </c>
       <c r="B7" t="n">
-        <v>79327</v>
+        <v>43383</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1176,34 +1176,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>201075</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Brunfläckig pärlemorfjäril</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Boloria selene</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Vitträskbäcken-Pålkem, Nb</t>
+          <t>Nymyran, Nymyran, Nb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>800743</v>
+        <v>800370</v>
       </c>
       <c r="R7" t="n">
-        <v>7374103</v>
+        <v>7374209</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1230,12 +1230,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2022-09-27</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2022-09-27</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1250,15 +1250,112 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>110049223</v>
+      </c>
+      <c r="B8" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Vitträskbäcken-Pålkem, Nb</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>800743</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7374103</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2022-09-27</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2022-09-27</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
           <t>Robert Sandberg</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
+      <c r="AX8" t="inlineStr">
         <is>
           <t>per-erik mukka</t>
         </is>
       </c>
-      <c r="AY7" t="inlineStr"/>
+      <c r="AY8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 51957-2025 artfynd.xlsx
+++ b/artfynd/A 51957-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104157791</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -871,6 +881,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110049228</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -968,6 +983,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110049292</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1065,6 +1085,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110049524</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1162,6 +1187,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110049532</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1259,6 +1289,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135449034</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1356,8 +1391,22 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110049223</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 51957-2025 artfynd.xlsx
+++ b/artfynd/A 51957-2025 artfynd.xlsx
@@ -1198,7 +1198,7 @@
         <v>135449034</v>
       </c>
       <c r="B7" t="n">
-        <v>43383</v>
+        <v>43388</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 51957-2025 artfynd.xlsx
+++ b/artfynd/A 51957-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ7"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1195,10 +1195,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>110049223</v>
+        <v>135449034</v>
       </c>
       <c r="B7" t="n">
-        <v>79327</v>
+        <v>43388</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1206,34 +1206,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>201075</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Brunfläckig pärlemorfjäril</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Boloria selene</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Vitträskbäcken-Pålkem, Nb</t>
+          <t>Nymyran, Nymyran, Nb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>800743</v>
+        <v>800370</v>
       </c>
       <c r="R7" t="n">
-        <v>7374103</v>
+        <v>7374209</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1260,12 +1260,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2022-09-27</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2022-09-27</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1280,16 +1280,118 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Robert Sandberg</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135449034</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>110049223</v>
+      </c>
+      <c r="B8" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Vitträskbäcken-Pålkem, Nb</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>800743</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7374103</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2022-09-27</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2022-09-27</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Robert Sandberg</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>per-erik mukka</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/110049223</t>
         </is>
@@ -1303,6 +1405,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 51957-2025 artfynd.xlsx
+++ b/artfynd/A 51957-2025 artfynd.xlsx
@@ -1198,7 +1198,7 @@
         <v>135449034</v>
       </c>
       <c r="B7" t="n">
-        <v>43388</v>
+        <v>43390</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
